--- a/openspec/點檢人員_範例.xlsx
+++ b/openspec/點檢人員_範例.xlsx
@@ -397,51 +397,296 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G12"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>員編</v>
+        <v>部別</v>
       </c>
       <c r="B1" t="str">
+        <v>課別</v>
+      </c>
+      <c r="C1" t="str">
+        <v>工號</v>
+      </c>
+      <c r="D1" t="str">
         <v>姓名</v>
       </c>
-      <c r="C1" t="str">
-        <v>部別</v>
-      </c>
-      <c r="D1" t="str">
-        <v>課別</v>
-      </c>
       <c r="E1" t="str">
+        <v>職稱</v>
+      </c>
+      <c r="F1" t="str">
         <v>AD帳號</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>角色</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>A001</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>（請填姓名）</v>
+        <v/>
       </c>
       <c r="C2" t="str">
+        <v>wangki</v>
+      </c>
+      <c r="D2" t="str">
+        <v>王啟丞</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>wangki</v>
+      </c>
+      <c r="G2" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>chiajen</v>
+      </c>
+      <c r="D3" t="str">
+        <v>陳家蓁</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>chiajen</v>
+      </c>
+      <c r="G3" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>wej5217</v>
+      </c>
+      <c r="D4" t="str">
+        <v>王怡晶</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>wej5217</v>
+      </c>
+      <c r="G4" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>huiwen</v>
+      </c>
+      <c r="D5" t="str">
+        <v>黃慧文</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>huiwen</v>
+      </c>
+      <c r="G5" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>sophie</v>
+      </c>
+      <c r="D6" t="str">
+        <v>黃秀惠</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>sophie</v>
+      </c>
+      <c r="G6" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>pyhpyh</v>
+      </c>
+      <c r="D7" t="str">
+        <v>彭仰徽</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>pyhpyh</v>
+      </c>
+      <c r="G7" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>jolin</v>
+      </c>
+      <c r="D8" t="str">
+        <v>林秀真</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>jolin</v>
+      </c>
+      <c r="G8" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>chun</v>
+      </c>
+      <c r="D9" t="str">
+        <v>鄭怡君</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>chun</v>
+      </c>
+      <c r="G9" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>joseph.wu</v>
+      </c>
+      <c r="D10" t="str">
+        <v>吳培根</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>joseph.wu</v>
+      </c>
+      <c r="G10" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>chendino</v>
+      </c>
+      <c r="D11" t="str">
+        <v>陳紀源</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>chendino</v>
+      </c>
+      <c r="G11" t="str">
+        <v>管理者</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>營運一部</v>
       </c>
-      <c r="D2" t="str">
+      <c r="B12" t="str">
         <v>北一課</v>
       </c>
-      <c r="E2" t="str">
-        <v>（請填你的AD帳號）</v>
-      </c>
-      <c r="F2" t="str">
-        <v>管理者</v>
+      <c r="C12" t="str">
+        <v>E001</v>
+      </c>
+      <c r="D12" t="str">
+        <v>（範例）張三</v>
+      </c>
+      <c r="E12" t="str">
+        <v>稽核員</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
   </ignoredErrors>
 </worksheet>
 </file>